--- a/Master_Pagos.xlsx
+++ b/Master_Pagos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TIP\Desktop\DASHBOARD_UCAL_25.1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{97A24A76-ABB6-44CA-8EED-B03593F81714}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1111AD7D-DE82-4665-9E70-0D6DD751206C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8427" uniqueCount="1098">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8462" uniqueCount="1102">
   <si>
     <t>ID PROMETEO</t>
   </si>
@@ -3325,6 +3325,18 @@
   </si>
   <si>
     <t>FLORES AQUINO</t>
+  </si>
+  <si>
+    <t>DAMARIS DANIELA</t>
+  </si>
+  <si>
+    <t>CHUPAYO FERNANDEZ</t>
+  </si>
+  <si>
+    <t>JOSSY VILMA</t>
+  </si>
+  <si>
+    <t>RAMOS ORTIZ</t>
   </si>
 </sst>
 </file>
@@ -3785,7 +3797,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D06DFE6-0680-4B05-BA75-00EC4F6BDFFC}">
-  <dimension ref="A1:V470"/>
+  <dimension ref="A1:V472"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:22" ht="47.4" thickBot="1">
@@ -35674,7 +35686,142 @@
         <v>652</v>
       </c>
     </row>
+    <row r="471" spans="1:22" ht="54" thickBot="1">
+      <c r="A471" s="2">
+        <v>4982191</v>
+      </c>
+      <c r="B471" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C471" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D471" s="4">
+        <v>45698</v>
+      </c>
+      <c r="E471" s="3" t="s">
+        <v>1098</v>
+      </c>
+      <c r="F471" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="G471" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H471" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="I471" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J471" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="K471" s="2">
+        <v>1</v>
+      </c>
+      <c r="L471" s="2">
+        <v>0</v>
+      </c>
+      <c r="M471" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N471" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="O471" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="P471" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q471" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="R471" s="2" t="s">
+        <v>763</v>
+      </c>
+      <c r="S471" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="T471" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="U471" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="V471" s="3" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="472" spans="1:22" ht="54" thickBot="1">
+      <c r="A472" s="2">
+        <v>728398</v>
+      </c>
+      <c r="B472" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C472" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D472" s="4">
+        <v>45698</v>
+      </c>
+      <c r="E472" s="3" t="s">
+        <v>1100</v>
+      </c>
+      <c r="F472" s="3" t="s">
+        <v>1101</v>
+      </c>
+      <c r="G472" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="H472" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I472" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J472" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="K472" s="2">
+        <v>1</v>
+      </c>
+      <c r="L472" s="2">
+        <v>0</v>
+      </c>
+      <c r="M472" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N472" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="O472" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="P472" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q472" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="R472" s="2" t="s">
+        <v>837</v>
+      </c>
+      <c r="S472" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="T472" s="7"/>
+      <c r="U472" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="V472" s="8" t="s">
+        <v>536</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Master_Pagos.xlsx
+++ b/Master_Pagos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TIP\Desktop\DASHBOARD_UCAL_25.1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1111AD7D-DE82-4665-9E70-0D6DD751206C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D55C5E8F-7CF6-4F07-943E-46366AADC93E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8462" uniqueCount="1102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8967" uniqueCount="1167">
   <si>
     <t>ID PROMETEO</t>
   </si>
@@ -3337,6 +3337,201 @@
   </si>
   <si>
     <t>RAMOS ORTIZ</t>
+  </si>
+  <si>
+    <t>KEVIN CRIS</t>
+  </si>
+  <si>
+    <t>ARONI NAVARRO</t>
+  </si>
+  <si>
+    <t>PAGO COMPLETO</t>
+  </si>
+  <si>
+    <t>ANGELY DEL MILAGRO</t>
+  </si>
+  <si>
+    <t>LIZANA TRIVEÑO</t>
+  </si>
+  <si>
+    <t>MATIAS ALONSO</t>
+  </si>
+  <si>
+    <t>RONDON GONZALES</t>
+  </si>
+  <si>
+    <t>innovacion</t>
+  </si>
+  <si>
+    <t>ARANCIBIA PEÑA</t>
+  </si>
+  <si>
+    <t>metodologia</t>
+  </si>
+  <si>
+    <t>PAGO FRACCIONADO</t>
+  </si>
+  <si>
+    <t>SAMANTA FERNANDA</t>
+  </si>
+  <si>
+    <t>LOJA DAVILA</t>
+  </si>
+  <si>
+    <t>MILENE NICOLE</t>
+  </si>
+  <si>
+    <t>QUISPE HUAYANTUPA</t>
+  </si>
+  <si>
+    <t>TIRSA GRASIEL MARIAM</t>
+  </si>
+  <si>
+    <t>SOLIS PALACIOS</t>
+  </si>
+  <si>
+    <t>NICOLE ANGELINA</t>
+  </si>
+  <si>
+    <t>PHILLIPS RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>VALENTINA</t>
+  </si>
+  <si>
+    <t>ARANCIBIA GARCIA</t>
+  </si>
+  <si>
+    <t>NICOLE MARICIELO</t>
+  </si>
+  <si>
+    <t>ORE ROCA</t>
+  </si>
+  <si>
+    <t>EDDY GIAN PIER</t>
+  </si>
+  <si>
+    <t>REYES DIAZ</t>
+  </si>
+  <si>
+    <t>LE GUSTA UCAL</t>
+  </si>
+  <si>
+    <t>PAOLA</t>
+  </si>
+  <si>
+    <t>ARIAS LOMAS</t>
+  </si>
+  <si>
+    <t>ANDREA NICOLE</t>
+  </si>
+  <si>
+    <t>CAMPANA CHAVEZ</t>
+  </si>
+  <si>
+    <t>LE GUSTA LA MALLA CURRICULAR</t>
+  </si>
+  <si>
+    <t>KATHERIN ESTHER</t>
+  </si>
+  <si>
+    <t>AMASIFUEN FERNANDEZ</t>
+  </si>
+  <si>
+    <t>Nocturno - Psicologia</t>
+  </si>
+  <si>
+    <t>LE GUSTA LA UNIVRSIDAD Y HORARIOS</t>
+  </si>
+  <si>
+    <t>JOSE JESUS</t>
+  </si>
+  <si>
+    <t>AGUIRRE PARIASA</t>
+  </si>
+  <si>
+    <t>LE GUSTA LA UNIVERSIDAD</t>
+  </si>
+  <si>
+    <t>KIARA VALESKA</t>
+  </si>
+  <si>
+    <t>TORRES BENAVENTE</t>
+  </si>
+  <si>
+    <t>Fiorella Lanegra</t>
+  </si>
+  <si>
+    <t>Referente de 71177047 ANGELES IVANNA DANCE HERNANDEZ</t>
+  </si>
+  <si>
+    <t>JHASSYRA MARIANA</t>
+  </si>
+  <si>
+    <t>CHUMPITAZ HERRERA</t>
+  </si>
+  <si>
+    <t>SOLANO DÍAZ</t>
+  </si>
+  <si>
+    <t>CARLOS FERNANDO</t>
+  </si>
+  <si>
+    <t>RAFAEL RICARDO</t>
+  </si>
+  <si>
+    <t>LEIVA GUERRA</t>
+  </si>
+  <si>
+    <t>Natalia Ugarte</t>
+  </si>
+  <si>
+    <t>tercera carrera</t>
+  </si>
+  <si>
+    <t>JOSE FERNANDO</t>
+  </si>
+  <si>
+    <t>ZEVALLOS SILVA</t>
+  </si>
+  <si>
+    <t>1ra boleta 500</t>
+  </si>
+  <si>
+    <t>GLADYS DEL PILAR</t>
+  </si>
+  <si>
+    <t>ROMERO GAMBOA</t>
+  </si>
+  <si>
+    <t>QUIERE LICENCIAMIENTO</t>
+  </si>
+  <si>
+    <t>ADRIAN JESUS</t>
+  </si>
+  <si>
+    <t>MAMANI BURGOS</t>
+  </si>
+  <si>
+    <t>EDU KENYI</t>
+  </si>
+  <si>
+    <t>PALACIOS OLORTEGUI</t>
+  </si>
+  <si>
+    <t>se traslada de Senati</t>
+  </si>
+  <si>
+    <t>MILAGROS MARIA PAZ</t>
+  </si>
+  <si>
+    <t>RADA PAREDES</t>
+  </si>
+  <si>
+    <t>ALISSON SHAKIRA</t>
+  </si>
+  <si>
+    <t>MALDONADO MATA</t>
   </si>
 </sst>
 </file>
@@ -3797,7 +3992,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D06DFE6-0680-4B05-BA75-00EC4F6BDFFC}">
-  <dimension ref="A1:V472"/>
+  <dimension ref="A1:X498"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:22" ht="47.4" thickBot="1">
@@ -35282,7 +35477,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="465" spans="1:22" ht="54" thickBot="1">
+    <row r="465" spans="1:24" ht="54" thickBot="1">
       <c r="A465" s="2">
         <v>3291366</v>
       </c>
@@ -35350,7 +35545,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="466" spans="1:22" ht="67.2" thickBot="1">
+    <row r="466" spans="1:24" ht="67.2" thickBot="1">
       <c r="A466" s="2">
         <v>4678748</v>
       </c>
@@ -35418,7 +35613,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="467" spans="1:22" ht="67.2" thickBot="1">
+    <row r="467" spans="1:24" ht="67.2" thickBot="1">
       <c r="A467" s="2">
         <v>4837517</v>
       </c>
@@ -35482,7 +35677,7 @@
       </c>
       <c r="V467" s="7"/>
     </row>
-    <row r="468" spans="1:22" ht="54" thickBot="1">
+    <row r="468" spans="1:24" ht="54" thickBot="1">
       <c r="A468" s="2">
         <v>1541761</v>
       </c>
@@ -35550,7 +35745,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="469" spans="1:22" ht="54" thickBot="1">
+    <row r="469" spans="1:24" ht="54" thickBot="1">
       <c r="A469" s="2">
         <v>4971719</v>
       </c>
@@ -35618,7 +35813,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="470" spans="1:22" ht="54" thickBot="1">
+    <row r="470" spans="1:24" ht="54" thickBot="1">
       <c r="A470" s="2">
         <v>4997590</v>
       </c>
@@ -35686,7 +35881,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="471" spans="1:22" ht="54" thickBot="1">
+    <row r="471" spans="1:24" ht="54" thickBot="1">
       <c r="A471" s="2">
         <v>4982191</v>
       </c>
@@ -35754,7 +35949,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="472" spans="1:22" ht="54" thickBot="1">
+    <row r="472" spans="1:24" ht="54" thickBot="1">
       <c r="A472" s="2">
         <v>728398</v>
       </c>
@@ -35818,6 +36013,1904 @@
       </c>
       <c r="V472" s="8" t="s">
         <v>536</v>
+      </c>
+    </row>
+    <row r="473" spans="1:24" ht="54" thickBot="1">
+      <c r="A473" s="2">
+        <v>1990115</v>
+      </c>
+      <c r="B473" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C473" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D473" s="4">
+        <v>45699</v>
+      </c>
+      <c r="E473" s="3" t="s">
+        <v>1102</v>
+      </c>
+      <c r="F473" s="3" t="s">
+        <v>1103</v>
+      </c>
+      <c r="G473" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H473" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I473" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J473" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="K473" s="2">
+        <v>0</v>
+      </c>
+      <c r="L473" s="2">
+        <v>1</v>
+      </c>
+      <c r="M473" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="N473" s="3" t="s">
+        <v>777</v>
+      </c>
+      <c r="O473" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="P473" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q473" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="R473" s="2" t="s">
+        <v>837</v>
+      </c>
+      <c r="S473" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="T473" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="U473" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="V473" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="W473" s="3">
+        <v>0</v>
+      </c>
+      <c r="X473" s="3" t="s">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="474" spans="1:24" ht="54" thickBot="1">
+      <c r="A474" s="2">
+        <v>4963807</v>
+      </c>
+      <c r="B474" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C474" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D474" s="4">
+        <v>45699</v>
+      </c>
+      <c r="E474" s="3" t="s">
+        <v>1105</v>
+      </c>
+      <c r="F474" s="3" t="s">
+        <v>1106</v>
+      </c>
+      <c r="G474" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="H474" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I474" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J474" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K474" s="2">
+        <v>0</v>
+      </c>
+      <c r="L474" s="2">
+        <v>0</v>
+      </c>
+      <c r="M474" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="N474" s="3" t="s">
+        <v>777</v>
+      </c>
+      <c r="O474" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="P474" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q474" s="2" t="s">
+        <v>944</v>
+      </c>
+      <c r="R474" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="S474" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="T474" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="U474" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="V474" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="W474" s="7"/>
+      <c r="X474" s="3" t="s">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="475" spans="1:24" ht="54" thickBot="1">
+      <c r="A475" s="2">
+        <v>4941138</v>
+      </c>
+      <c r="B475" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C475" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D475" s="4">
+        <v>45699</v>
+      </c>
+      <c r="E475" s="3" t="s">
+        <v>1107</v>
+      </c>
+      <c r="F475" s="3" t="s">
+        <v>1108</v>
+      </c>
+      <c r="G475" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="H475" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I475" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J475" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="K475" s="2">
+        <v>1</v>
+      </c>
+      <c r="L475" s="2">
+        <v>0</v>
+      </c>
+      <c r="M475" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N475" s="3" t="s">
+        <v>1093</v>
+      </c>
+      <c r="O475" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="P475" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q475" s="2" t="s">
+        <v>763</v>
+      </c>
+      <c r="R475" s="2" t="s">
+        <v>763</v>
+      </c>
+      <c r="S475" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="T475" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="U475" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="V475" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="W475" s="3" t="s">
+        <v>1109</v>
+      </c>
+      <c r="X475" s="3" t="s">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="476" spans="1:24" ht="54" thickBot="1">
+      <c r="A476" s="2">
+        <v>1996908</v>
+      </c>
+      <c r="B476" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C476" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D476" s="4">
+        <v>45699</v>
+      </c>
+      <c r="E476" s="3" t="s">
+        <v>1044</v>
+      </c>
+      <c r="F476" s="3" t="s">
+        <v>1110</v>
+      </c>
+      <c r="G476" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="H476" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I476" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J476" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K476" s="2">
+        <v>0</v>
+      </c>
+      <c r="L476" s="2">
+        <v>0</v>
+      </c>
+      <c r="M476" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="N476" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="O476" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="P476" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q476" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="R476" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="S476" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="T476" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="U476" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="V476" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="W476" s="3" t="s">
+        <v>1111</v>
+      </c>
+      <c r="X476" s="3" t="s">
+        <v>1112</v>
+      </c>
+    </row>
+    <row r="477" spans="1:24" ht="40.799999999999997" thickBot="1">
+      <c r="A477" s="2">
+        <v>4975774</v>
+      </c>
+      <c r="B477" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C477" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D477" s="4">
+        <v>45699</v>
+      </c>
+      <c r="E477" s="3" t="s">
+        <v>1113</v>
+      </c>
+      <c r="F477" s="3" t="s">
+        <v>1114</v>
+      </c>
+      <c r="G477" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="H477" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I477" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J477" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K477" s="2">
+        <v>0</v>
+      </c>
+      <c r="L477" s="2">
+        <v>0</v>
+      </c>
+      <c r="M477" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N477" s="3" t="s">
+        <v>892</v>
+      </c>
+      <c r="O477" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="P477" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q477" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="R477" s="2" t="s">
+        <v>763</v>
+      </c>
+      <c r="S477" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="T477" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="U477" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="V477" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="W477" s="3" t="s">
+        <v>1111</v>
+      </c>
+      <c r="X477" s="3" t="s">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="478" spans="1:24" ht="54" thickBot="1">
+      <c r="A478" s="2">
+        <v>5015435</v>
+      </c>
+      <c r="B478" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C478" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D478" s="4">
+        <v>45699</v>
+      </c>
+      <c r="E478" s="3" t="s">
+        <v>1115</v>
+      </c>
+      <c r="F478" s="3" t="s">
+        <v>1116</v>
+      </c>
+      <c r="G478" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="H478" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I478" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J478" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K478" s="2">
+        <v>0</v>
+      </c>
+      <c r="L478" s="2">
+        <v>0</v>
+      </c>
+      <c r="M478" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="N478" s="3" t="s">
+        <v>777</v>
+      </c>
+      <c r="O478" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="P478" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q478" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="R478" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="S478" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="T478" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="U478" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="V478" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="W478" s="7"/>
+      <c r="X478" s="3" t="s">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="479" spans="1:24" ht="54" thickBot="1">
+      <c r="A479" s="2">
+        <v>4982817</v>
+      </c>
+      <c r="B479" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C479" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D479" s="4">
+        <v>45700</v>
+      </c>
+      <c r="E479" s="3" t="s">
+        <v>1117</v>
+      </c>
+      <c r="F479" s="3" t="s">
+        <v>1118</v>
+      </c>
+      <c r="G479" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="H479" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I479" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J479" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K479" s="2">
+        <v>0</v>
+      </c>
+      <c r="L479" s="2">
+        <v>0</v>
+      </c>
+      <c r="M479" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="N479" s="3" t="s">
+        <v>777</v>
+      </c>
+      <c r="O479" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="P479" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q479" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="R479" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="S479" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="T479" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="U479" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="V479" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="W479" s="7"/>
+      <c r="X479" s="3" t="s">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="480" spans="1:24" ht="54" thickBot="1">
+      <c r="A480" s="2">
+        <v>4861888</v>
+      </c>
+      <c r="B480" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C480" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D480" s="4">
+        <v>45700</v>
+      </c>
+      <c r="E480" s="3" t="s">
+        <v>1119</v>
+      </c>
+      <c r="F480" s="3" t="s">
+        <v>1120</v>
+      </c>
+      <c r="G480" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H480" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I480" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J480" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K480" s="2">
+        <v>0</v>
+      </c>
+      <c r="L480" s="2">
+        <v>0</v>
+      </c>
+      <c r="M480" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="N480" s="3" t="s">
+        <v>777</v>
+      </c>
+      <c r="O480" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="P480" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q480" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="R480" s="2" t="s">
+        <v>837</v>
+      </c>
+      <c r="S480" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="T480" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="U480" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="V480" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="W480" s="7"/>
+      <c r="X480" s="3" t="s">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="481" spans="1:24" ht="80.400000000000006" thickBot="1">
+      <c r="A481" s="2">
+        <v>1323339</v>
+      </c>
+      <c r="B481" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C481" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D481" s="4">
+        <v>45700</v>
+      </c>
+      <c r="E481" s="3" t="s">
+        <v>1121</v>
+      </c>
+      <c r="F481" s="3" t="s">
+        <v>1122</v>
+      </c>
+      <c r="G481" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="H481" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I481" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J481" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K481" s="2">
+        <v>0</v>
+      </c>
+      <c r="L481" s="2">
+        <v>0</v>
+      </c>
+      <c r="M481" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="N481" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="O481" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="P481" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q481" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="R481" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="S481" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="T481" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="U481" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="V481" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="W481" s="3" t="s">
+        <v>1111</v>
+      </c>
+      <c r="X481" s="3" t="s">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="482" spans="1:24" ht="54" thickBot="1">
+      <c r="A482" s="2">
+        <v>4985273</v>
+      </c>
+      <c r="B482" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C482" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D482" s="4">
+        <v>45700</v>
+      </c>
+      <c r="E482" s="3" t="s">
+        <v>1123</v>
+      </c>
+      <c r="F482" s="3" t="s">
+        <v>1124</v>
+      </c>
+      <c r="G482" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="H482" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I482" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J482" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K482" s="2">
+        <v>0</v>
+      </c>
+      <c r="L482" s="2">
+        <v>0</v>
+      </c>
+      <c r="M482" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N482" s="3" t="s">
+        <v>777</v>
+      </c>
+      <c r="O482" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="P482" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q482" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="R482" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="S482" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="T482" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="U482" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="V482" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="W482" s="7"/>
+      <c r="X482" s="3" t="s">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="483" spans="1:24" ht="40.799999999999997" thickBot="1">
+      <c r="A483" s="2">
+        <v>1446984</v>
+      </c>
+      <c r="B483" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C483" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D483" s="4">
+        <v>45700</v>
+      </c>
+      <c r="E483" s="3" t="s">
+        <v>1125</v>
+      </c>
+      <c r="F483" s="3" t="s">
+        <v>1126</v>
+      </c>
+      <c r="G483" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="H483" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I483" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J483" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K483" s="2">
+        <v>0</v>
+      </c>
+      <c r="L483" s="2">
+        <v>0</v>
+      </c>
+      <c r="M483" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="N483" s="3" t="s">
+        <v>475</v>
+      </c>
+      <c r="O483" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="P483" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q483" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="R483" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="S483" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="T483" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="U483" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="V483" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="W483" s="3" t="s">
+        <v>1127</v>
+      </c>
+      <c r="X483" s="3" t="s">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="484" spans="1:24" ht="40.799999999999997" thickBot="1">
+      <c r="A484" s="2">
+        <v>5016050</v>
+      </c>
+      <c r="B484" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C484" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D484" s="4">
+        <v>45700</v>
+      </c>
+      <c r="E484" s="3" t="s">
+        <v>1128</v>
+      </c>
+      <c r="F484" s="3" t="s">
+        <v>1129</v>
+      </c>
+      <c r="G484" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="H484" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="I484" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="J484" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K484" s="2">
+        <v>0</v>
+      </c>
+      <c r="L484" s="2">
+        <v>0</v>
+      </c>
+      <c r="M484" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N484" s="3" t="s">
+        <v>892</v>
+      </c>
+      <c r="O484" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="P484" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q484" s="2" t="s">
+        <v>763</v>
+      </c>
+      <c r="R484" s="2" t="s">
+        <v>763</v>
+      </c>
+      <c r="S484" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="T484" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="U484" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="V484" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="W484" s="3" t="s">
+        <v>1111</v>
+      </c>
+      <c r="X484" s="3" t="s">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="485" spans="1:24" ht="54" thickBot="1">
+      <c r="A485" s="2">
+        <v>5009089</v>
+      </c>
+      <c r="B485" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C485" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D485" s="4">
+        <v>45700</v>
+      </c>
+      <c r="E485" s="3" t="s">
+        <v>1130</v>
+      </c>
+      <c r="F485" s="3" t="s">
+        <v>1131</v>
+      </c>
+      <c r="G485" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="H485" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I485" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J485" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="K485" s="2">
+        <v>1</v>
+      </c>
+      <c r="L485" s="2">
+        <v>0</v>
+      </c>
+      <c r="M485" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N485" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="O485" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="P485" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q485" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="R485" s="2" t="s">
+        <v>763</v>
+      </c>
+      <c r="S485" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="T485" s="7"/>
+      <c r="U485" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="V485" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="W485" s="3" t="s">
+        <v>1132</v>
+      </c>
+      <c r="X485" s="3" t="s">
+        <v>1112</v>
+      </c>
+    </row>
+    <row r="486" spans="1:24" ht="67.2" thickBot="1">
+      <c r="A486" s="2">
+        <v>4992828</v>
+      </c>
+      <c r="B486" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C486" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D486" s="4">
+        <v>45700</v>
+      </c>
+      <c r="E486" s="3" t="s">
+        <v>1133</v>
+      </c>
+      <c r="F486" s="3" t="s">
+        <v>1134</v>
+      </c>
+      <c r="G486" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="H486" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="I486" s="3" t="s">
+        <v>1135</v>
+      </c>
+      <c r="J486" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K486" s="2">
+        <v>0</v>
+      </c>
+      <c r="L486" s="2">
+        <v>0</v>
+      </c>
+      <c r="M486" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N486" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="O486" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="P486" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q486" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="R486" s="2" t="s">
+        <v>763</v>
+      </c>
+      <c r="S486" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="T486" s="7"/>
+      <c r="U486" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="V486" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="W486" s="3" t="s">
+        <v>1136</v>
+      </c>
+      <c r="X486" s="3" t="s">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="487" spans="1:24" ht="54" thickBot="1">
+      <c r="A487" s="2">
+        <v>4899431</v>
+      </c>
+      <c r="B487" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C487" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D487" s="4">
+        <v>45701</v>
+      </c>
+      <c r="E487" s="3" t="s">
+        <v>1137</v>
+      </c>
+      <c r="F487" s="3" t="s">
+        <v>1138</v>
+      </c>
+      <c r="G487" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H487" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I487" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J487" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K487" s="2">
+        <v>0</v>
+      </c>
+      <c r="L487" s="2">
+        <v>0</v>
+      </c>
+      <c r="M487" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="N487" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="O487" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="P487" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q487" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="R487" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="S487" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="T487" s="7"/>
+      <c r="U487" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="V487" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="W487" s="3" t="s">
+        <v>1139</v>
+      </c>
+      <c r="X487" s="3" t="s">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="488" spans="1:24" ht="93.6" thickBot="1">
+      <c r="A488" s="2">
+        <v>4521815</v>
+      </c>
+      <c r="B488" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C488" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D488" s="4">
+        <v>45701</v>
+      </c>
+      <c r="E488" s="3" t="s">
+        <v>1140</v>
+      </c>
+      <c r="F488" s="3" t="s">
+        <v>1141</v>
+      </c>
+      <c r="G488" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="H488" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="I488" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J488" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K488" s="2">
+        <v>0</v>
+      </c>
+      <c r="L488" s="2">
+        <v>0</v>
+      </c>
+      <c r="M488" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N488" s="3" t="s">
+        <v>777</v>
+      </c>
+      <c r="O488" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="P488" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q488" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="R488" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="S488" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="T488" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="U488" s="3" t="s">
+        <v>1142</v>
+      </c>
+      <c r="V488" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="W488" s="3" t="s">
+        <v>1143</v>
+      </c>
+      <c r="X488" s="3" t="s">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="489" spans="1:24" ht="54" thickBot="1">
+      <c r="A489" s="2">
+        <v>5014268</v>
+      </c>
+      <c r="B489" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C489" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D489" s="4">
+        <v>45701</v>
+      </c>
+      <c r="E489" s="3" t="s">
+        <v>1144</v>
+      </c>
+      <c r="F489" s="3" t="s">
+        <v>1145</v>
+      </c>
+      <c r="G489" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="H489" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I489" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J489" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="K489" s="2">
+        <v>1</v>
+      </c>
+      <c r="L489" s="2">
+        <v>0</v>
+      </c>
+      <c r="M489" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N489" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="O489" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="P489" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q489" s="2" t="s">
+        <v>763</v>
+      </c>
+      <c r="R489" s="2" t="s">
+        <v>763</v>
+      </c>
+      <c r="S489" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="T489" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="U489" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="V489" s="3" t="s">
+        <v>472</v>
+      </c>
+      <c r="W489" s="7"/>
+      <c r="X489" s="3" t="s">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="490" spans="1:24" ht="54" thickBot="1">
+      <c r="A490" s="2">
+        <v>1946333</v>
+      </c>
+      <c r="B490" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C490" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D490" s="4">
+        <v>45701</v>
+      </c>
+      <c r="E490" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="F490" s="3" t="s">
+        <v>1146</v>
+      </c>
+      <c r="G490" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="H490" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I490" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J490" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="K490" s="2">
+        <v>1</v>
+      </c>
+      <c r="L490" s="2">
+        <v>0</v>
+      </c>
+      <c r="M490" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N490" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="O490" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="P490" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q490" s="2" t="s">
+        <v>1030</v>
+      </c>
+      <c r="R490" s="2" t="s">
+        <v>1030</v>
+      </c>
+      <c r="S490" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="T490" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="U490" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="V490" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="W490" s="3" t="s">
+        <v>1111</v>
+      </c>
+      <c r="X490" s="3" t="s">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="491" spans="1:24" ht="40.799999999999997" thickBot="1">
+      <c r="A491" s="2">
+        <v>5015421</v>
+      </c>
+      <c r="B491" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C491" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D491" s="4">
+        <v>45701</v>
+      </c>
+      <c r="E491" s="3" t="s">
+        <v>1147</v>
+      </c>
+      <c r="F491" s="3" t="s">
+        <v>1106</v>
+      </c>
+      <c r="G491" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="H491" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="I491" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J491" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K491" s="2">
+        <v>0</v>
+      </c>
+      <c r="L491" s="2">
+        <v>1</v>
+      </c>
+      <c r="M491" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="N491" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="O491" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="P491" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q491" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="R491" s="2" t="s">
+        <v>837</v>
+      </c>
+      <c r="S491" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="T491" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="U491" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="V491" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="W491" s="3">
+        <v>0</v>
+      </c>
+      <c r="X491" s="3" t="s">
+        <v>1112</v>
+      </c>
+    </row>
+    <row r="492" spans="1:24" ht="40.799999999999997" thickBot="1">
+      <c r="A492" s="2">
+        <v>4987115</v>
+      </c>
+      <c r="B492" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C492" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D492" s="4">
+        <v>45701</v>
+      </c>
+      <c r="E492" s="3" t="s">
+        <v>1148</v>
+      </c>
+      <c r="F492" s="3" t="s">
+        <v>1149</v>
+      </c>
+      <c r="G492" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="H492" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I492" s="3" t="s">
+        <v>1135</v>
+      </c>
+      <c r="J492" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K492" s="2">
+        <v>0</v>
+      </c>
+      <c r="L492" s="2">
+        <v>0</v>
+      </c>
+      <c r="M492" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="N492" s="3" t="s">
+        <v>892</v>
+      </c>
+      <c r="O492" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="P492" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q492" s="2" t="s">
+        <v>763</v>
+      </c>
+      <c r="R492" s="2" t="s">
+        <v>763</v>
+      </c>
+      <c r="S492" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="T492" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="U492" s="3" t="s">
+        <v>1150</v>
+      </c>
+      <c r="V492" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="W492" s="3" t="s">
+        <v>1151</v>
+      </c>
+      <c r="X492" s="3" t="s">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="493" spans="1:24" ht="54" thickBot="1">
+      <c r="A493" s="2">
+        <v>5018756</v>
+      </c>
+      <c r="B493" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C493" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D493" s="4">
+        <v>45702</v>
+      </c>
+      <c r="E493" s="3" t="s">
+        <v>1152</v>
+      </c>
+      <c r="F493" s="3" t="s">
+        <v>1153</v>
+      </c>
+      <c r="G493" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H493" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I493" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J493" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K493" s="2">
+        <v>0</v>
+      </c>
+      <c r="L493" s="2">
+        <v>0</v>
+      </c>
+      <c r="M493" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="N493" s="3" t="s">
+        <v>777</v>
+      </c>
+      <c r="O493" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="P493" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q493" s="2" t="s">
+        <v>944</v>
+      </c>
+      <c r="R493" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="S493" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="T493" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="U493" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="V493" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="W493" s="3" t="s">
+        <v>1154</v>
+      </c>
+      <c r="X493" s="3" t="s">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="494" spans="1:24" ht="54" thickBot="1">
+      <c r="A494" s="2">
+        <v>443962</v>
+      </c>
+      <c r="B494" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C494" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D494" s="4">
+        <v>45702</v>
+      </c>
+      <c r="E494" s="3" t="s">
+        <v>1155</v>
+      </c>
+      <c r="F494" s="3" t="s">
+        <v>1156</v>
+      </c>
+      <c r="G494" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="H494" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="I494" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J494" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="K494" s="2">
+        <v>0</v>
+      </c>
+      <c r="L494" s="2">
+        <v>0</v>
+      </c>
+      <c r="M494" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N494" s="3" t="s">
+        <v>475</v>
+      </c>
+      <c r="O494" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="P494" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q494" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="R494" s="2" t="s">
+        <v>763</v>
+      </c>
+      <c r="S494" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="T494" s="7"/>
+      <c r="U494" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="V494" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="W494" s="3" t="s">
+        <v>1157</v>
+      </c>
+      <c r="X494" s="3" t="s">
+        <v>1112</v>
+      </c>
+    </row>
+    <row r="495" spans="1:24" ht="54" thickBot="1">
+      <c r="A495" s="2">
+        <v>4721471</v>
+      </c>
+      <c r="B495" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C495" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D495" s="4">
+        <v>45702</v>
+      </c>
+      <c r="E495" s="3" t="s">
+        <v>1158</v>
+      </c>
+      <c r="F495" s="3" t="s">
+        <v>1159</v>
+      </c>
+      <c r="G495" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="H495" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I495" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J495" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="K495" s="2">
+        <v>1</v>
+      </c>
+      <c r="L495" s="2">
+        <v>0</v>
+      </c>
+      <c r="M495" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N495" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="O495" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="P495" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q495" s="2" t="s">
+        <v>944</v>
+      </c>
+      <c r="R495" s="2" t="s">
+        <v>763</v>
+      </c>
+      <c r="S495" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="T495" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="U495" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="V495" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="W495" s="7"/>
+      <c r="X495" s="3" t="s">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="496" spans="1:24" ht="54" thickBot="1">
+      <c r="A496" s="2">
+        <v>1552430</v>
+      </c>
+      <c r="B496" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C496" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D496" s="4">
+        <v>45703</v>
+      </c>
+      <c r="E496" s="3" t="s">
+        <v>1160</v>
+      </c>
+      <c r="F496" s="3" t="s">
+        <v>1161</v>
+      </c>
+      <c r="G496" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="H496" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="I496" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J496" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="K496" s="2">
+        <v>1</v>
+      </c>
+      <c r="L496" s="2">
+        <v>0</v>
+      </c>
+      <c r="M496" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N496" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="O496" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="P496" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q496" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="R496" s="2" t="s">
+        <v>763</v>
+      </c>
+      <c r="S496" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="T496" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="U496" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="V496" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="W496" s="3" t="s">
+        <v>1162</v>
+      </c>
+      <c r="X496" s="3" t="s">
+        <v>1112</v>
+      </c>
+    </row>
+    <row r="497" spans="1:24" ht="40.799999999999997" thickBot="1">
+      <c r="A497" s="2">
+        <v>2864588</v>
+      </c>
+      <c r="B497" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C497" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D497" s="4">
+        <v>45704</v>
+      </c>
+      <c r="E497" s="3" t="s">
+        <v>1163</v>
+      </c>
+      <c r="F497" s="3" t="s">
+        <v>1164</v>
+      </c>
+      <c r="G497" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="H497" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="I497" s="3" t="s">
+        <v>1135</v>
+      </c>
+      <c r="J497" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K497" s="2">
+        <v>0</v>
+      </c>
+      <c r="L497" s="2">
+        <v>0</v>
+      </c>
+      <c r="M497" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="N497" s="3" t="s">
+        <v>892</v>
+      </c>
+      <c r="O497" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="P497" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q497" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="R497" s="2" t="s">
+        <v>763</v>
+      </c>
+      <c r="S497" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="T497" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="U497" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="V497" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="W497" s="3" t="s">
+        <v>1111</v>
+      </c>
+      <c r="X497" s="3" t="s">
+        <v>1112</v>
+      </c>
+    </row>
+    <row r="498" spans="1:24" ht="54" thickBot="1">
+      <c r="A498" s="2">
+        <v>3292842</v>
+      </c>
+      <c r="B498" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C498" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D498" s="4">
+        <v>45704</v>
+      </c>
+      <c r="E498" s="3" t="s">
+        <v>1165</v>
+      </c>
+      <c r="F498" s="3" t="s">
+        <v>1166</v>
+      </c>
+      <c r="G498" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H498" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I498" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J498" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K498" s="2">
+        <v>0</v>
+      </c>
+      <c r="L498" s="2">
+        <v>0</v>
+      </c>
+      <c r="M498" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="N498" s="3" t="s">
+        <v>777</v>
+      </c>
+      <c r="O498" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="P498" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q498" s="2" t="s">
+        <v>944</v>
+      </c>
+      <c r="R498" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="S498" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="T498" s="7"/>
+      <c r="U498" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="V498" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="W498" s="7"/>
+      <c r="X498" s="3" t="s">
+        <v>1104</v>
       </c>
     </row>
   </sheetData>

--- a/Master_Pagos.xlsx
+++ b/Master_Pagos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TIP\Desktop\DASHBOARD_UCAL_25.1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0058311-5ECE-4E1C-8F95-B4789F055DC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBDCD8B6-C0E3-4F48-BCDC-468E09338E45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16382" uniqueCount="1865">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16397" uniqueCount="1867">
   <si>
     <t>ID PROMETEO</t>
   </si>
@@ -5629,6 +5629,12 @@
   </si>
   <si>
     <t>mathiaspolackch@gmail.com</t>
+  </si>
+  <si>
+    <t>DANIELA</t>
+  </si>
+  <si>
+    <t>LAU ALVAREZ</t>
   </si>
 </sst>
 </file>
@@ -6101,7 +6107,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D06DFE6-0680-4B05-BA75-00EC4F6BDFFC}">
-  <dimension ref="A1:BO499"/>
+  <dimension ref="A1:BO500"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:67" ht="70.2" thickBot="1">
@@ -100655,6 +100661,65 @@
         <v>1850</v>
       </c>
     </row>
+    <row r="500" spans="1:44" ht="54" thickBot="1">
+      <c r="A500" s="2">
+        <v>5026066</v>
+      </c>
+      <c r="B500" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C500" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D500" s="4">
+        <v>45706</v>
+      </c>
+      <c r="E500" s="3" t="s">
+        <v>1865</v>
+      </c>
+      <c r="F500" s="3" t="s">
+        <v>1866</v>
+      </c>
+      <c r="G500" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H500" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I500" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J500" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K500" s="2">
+        <v>0</v>
+      </c>
+      <c r="L500" s="2">
+        <v>0</v>
+      </c>
+      <c r="M500" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="N500" s="3" t="s">
+        <v>767</v>
+      </c>
+      <c r="O500" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="P500" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q500" s="2" t="s">
+        <v>934</v>
+      </c>
+      <c r="R500" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="S500" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/Master_Pagos.xlsx
+++ b/Master_Pagos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TIP\Desktop\DASHBOARD_UCAL_25.1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBDCD8B6-C0E3-4F48-BCDC-468E09338E45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A278887-EC91-4DAE-BA13-616E256A0F30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16397" uniqueCount="1867">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16530" uniqueCount="1881">
   <si>
     <t>ID PROMETEO</t>
   </si>
@@ -5635,6 +5635,48 @@
   </si>
   <si>
     <t>LAU ALVAREZ</t>
+  </si>
+  <si>
+    <t>ARIANA ABIGAIL</t>
+  </si>
+  <si>
+    <t>SANTOS HUAMANTUCO</t>
+  </si>
+  <si>
+    <t>ESTEFANNY NATALIA</t>
+  </si>
+  <si>
+    <t>CALDERON LINO</t>
+  </si>
+  <si>
+    <t>ALFREDO CARLOS DANIEL ARISTOTELES</t>
+  </si>
+  <si>
+    <t>GUERRA HUIRSE</t>
+  </si>
+  <si>
+    <t>MIA REBECA</t>
+  </si>
+  <si>
+    <t>RIVERA RUIZ</t>
+  </si>
+  <si>
+    <t>palanca 500</t>
+  </si>
+  <si>
+    <t>ADAN ISRAEL</t>
+  </si>
+  <si>
+    <t>VICENTE YLLESCAS</t>
+  </si>
+  <si>
+    <t>POOL ANDY</t>
+  </si>
+  <si>
+    <t>LOZANO HUAYLLACCAHUA</t>
+  </si>
+  <si>
+    <t>CARRERA NAZRA</t>
   </si>
 </sst>
 </file>
@@ -6107,7 +6149,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D06DFE6-0680-4B05-BA75-00EC4F6BDFFC}">
-  <dimension ref="A1:BO500"/>
+  <dimension ref="A1:BO507"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:67" ht="70.2" thickBot="1">
@@ -100720,6 +100762,512 @@
         <v>68</v>
       </c>
     </row>
+    <row r="501" spans="1:44" ht="54" thickBot="1">
+      <c r="A501" s="2">
+        <v>4938587</v>
+      </c>
+      <c r="B501" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C501" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D501" s="4">
+        <v>45707</v>
+      </c>
+      <c r="E501" s="3" t="s">
+        <v>1867</v>
+      </c>
+      <c r="F501" s="3" t="s">
+        <v>1868</v>
+      </c>
+      <c r="G501" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="H501" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I501" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J501" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K501" s="2">
+        <v>0</v>
+      </c>
+      <c r="L501" s="2">
+        <v>0</v>
+      </c>
+      <c r="M501" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="N501" s="3" t="s">
+        <v>767</v>
+      </c>
+      <c r="O501" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="P501" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q501" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="R501" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="S501" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="T501" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="U501" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="V501" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="W501" s="3">
+        <v>0</v>
+      </c>
+      <c r="X501" s="3" t="s">
+        <v>1094</v>
+      </c>
+    </row>
+    <row r="502" spans="1:44" ht="54" thickBot="1">
+      <c r="A502" s="2">
+        <v>5025537</v>
+      </c>
+      <c r="B502" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C502" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D502" s="4">
+        <v>45707</v>
+      </c>
+      <c r="E502" s="3" t="s">
+        <v>1869</v>
+      </c>
+      <c r="F502" s="3" t="s">
+        <v>1870</v>
+      </c>
+      <c r="G502" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="H502" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I502" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J502" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K502" s="2">
+        <v>0</v>
+      </c>
+      <c r="L502" s="2">
+        <v>0</v>
+      </c>
+      <c r="M502" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="N502" s="3" t="s">
+        <v>767</v>
+      </c>
+      <c r="O502" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="P502" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q502" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="R502" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="S502" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="T502" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="U502" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="V502" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="W502" s="7"/>
+      <c r="X502" s="3" t="s">
+        <v>1094</v>
+      </c>
+    </row>
+    <row r="503" spans="1:44" ht="67.2" thickBot="1">
+      <c r="A503" s="2">
+        <v>5028709</v>
+      </c>
+      <c r="B503" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C503" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D503" s="4">
+        <v>45707</v>
+      </c>
+      <c r="E503" s="3" t="s">
+        <v>1871</v>
+      </c>
+      <c r="F503" s="3" t="s">
+        <v>1872</v>
+      </c>
+      <c r="G503" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="H503" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I503" s="3" t="s">
+        <v>1121</v>
+      </c>
+      <c r="J503" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K503" s="2">
+        <v>0</v>
+      </c>
+      <c r="L503" s="2">
+        <v>0</v>
+      </c>
+      <c r="M503" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="N503" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="O503" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="P503" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q503" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="R503" s="2" t="s">
+        <v>753</v>
+      </c>
+      <c r="S503" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="T503" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="U503" s="3" t="s">
+        <v>1126</v>
+      </c>
+      <c r="V503" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="W503" s="7"/>
+      <c r="X503" s="3" t="s">
+        <v>1094</v>
+      </c>
+    </row>
+    <row r="504" spans="1:44" ht="54" thickBot="1">
+      <c r="A504" s="2">
+        <v>4783874</v>
+      </c>
+      <c r="B504" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C504" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D504" s="4">
+        <v>45707</v>
+      </c>
+      <c r="E504" s="3" t="s">
+        <v>1873</v>
+      </c>
+      <c r="F504" s="3" t="s">
+        <v>1874</v>
+      </c>
+      <c r="G504" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="H504" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I504" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J504" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K504" s="2">
+        <v>0</v>
+      </c>
+      <c r="L504" s="2">
+        <v>0</v>
+      </c>
+      <c r="M504" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="N504" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="O504" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="P504" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q504" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="R504" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="S504" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="T504" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="U504" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="V504" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="W504" s="3" t="s">
+        <v>1875</v>
+      </c>
+      <c r="X504" s="3" t="s">
+        <v>1094</v>
+      </c>
+    </row>
+    <row r="505" spans="1:44" ht="54" thickBot="1">
+      <c r="A505" s="2">
+        <v>5009057</v>
+      </c>
+      <c r="B505" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C505" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D505" s="4">
+        <v>45707</v>
+      </c>
+      <c r="E505" s="3" t="s">
+        <v>1876</v>
+      </c>
+      <c r="F505" s="3" t="s">
+        <v>1877</v>
+      </c>
+      <c r="G505" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H505" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I505" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J505" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="K505" s="2">
+        <v>1</v>
+      </c>
+      <c r="L505" s="2">
+        <v>0</v>
+      </c>
+      <c r="M505" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="N505" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="O505" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="P505" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q505" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="R505" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="S505" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="T505" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="U505" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="V505" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="W505" s="7"/>
+      <c r="X505" s="3" t="s">
+        <v>1094</v>
+      </c>
+    </row>
+    <row r="506" spans="1:44" ht="54" thickBot="1">
+      <c r="A506" s="2">
+        <v>1704578</v>
+      </c>
+      <c r="B506" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C506" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D506" s="4">
+        <v>45707</v>
+      </c>
+      <c r="E506" s="3" t="s">
+        <v>1878</v>
+      </c>
+      <c r="F506" s="3" t="s">
+        <v>1879</v>
+      </c>
+      <c r="G506" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H506" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="I506" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J506" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="K506" s="2">
+        <v>0</v>
+      </c>
+      <c r="L506" s="2">
+        <v>0</v>
+      </c>
+      <c r="M506" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="N506" s="3" t="s">
+        <v>767</v>
+      </c>
+      <c r="O506" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="P506" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q506" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="R506" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="S506" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="T506" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="U506" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="V506" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="W506" s="7"/>
+      <c r="X506" s="3" t="s">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="507" spans="1:44" ht="54" thickBot="1">
+      <c r="A507" s="2">
+        <v>3282566</v>
+      </c>
+      <c r="B507" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C507" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D507" s="4">
+        <v>45707</v>
+      </c>
+      <c r="E507" s="3" t="s">
+        <v>1865</v>
+      </c>
+      <c r="F507" s="3" t="s">
+        <v>1880</v>
+      </c>
+      <c r="G507" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="H507" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I507" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J507" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K507" s="2">
+        <v>0</v>
+      </c>
+      <c r="L507" s="2">
+        <v>0</v>
+      </c>
+      <c r="M507" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="N507" s="3" t="s">
+        <v>767</v>
+      </c>
+      <c r="O507" s="2" t="s">
+        <v>606</v>
+      </c>
+      <c r="P507" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="Q507" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="R507" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="S507" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="T507" s="7"/>
+      <c r="U507" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="V507" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="W507" s="7"/>
+      <c r="X507" s="3" t="s">
+        <v>1094</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
